--- a/90411_REPORT_BOTTEGA_04-01-2026.xlsx
+++ b/90411_REPORT_BOTTEGA_04-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="96">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 04/01/2026</t>
   </si>
   <si>
@@ -73,16 +107,22 @@
     <t>% TOT</t>
   </si>
   <si>
+    <t>50-004-011-000750</t>
+  </si>
+  <si>
+    <t>Punta Di Petto (Con Patate)</t>
+  </si>
+  <si>
     <t>50-004-011-001941</t>
   </si>
   <si>
     <t>Fiorentina Frollata</t>
   </si>
   <si>
-    <t>50-004-011-000750</t>
-  </si>
-  <si>
-    <t>Punta Di Petto (Con Patate)</t>
+    <t>50-004-011-000590</t>
+  </si>
+  <si>
+    <t>Filetto Bovino adulto</t>
   </si>
   <si>
     <t>50-004-011-000730</t>
@@ -97,10 +137,16 @@
     <t>Hamburger Di Chianina (Con Patate)</t>
   </si>
   <si>
-    <t>50-004-011-000590</t>
-  </si>
-  <si>
-    <t>Filetto Bovino adulto</t>
+    <t>50-004-011-001490</t>
+  </si>
+  <si>
+    <t>Controfiletto chianina</t>
+  </si>
+  <si>
+    <t>50-004-011-000740</t>
+  </si>
+  <si>
+    <t>Pulled Pork (Con Patate)</t>
   </si>
   <si>
     <t>50-004-011-000600</t>
@@ -109,12 +155,6 @@
     <t>Grigliata Mista</t>
   </si>
   <si>
-    <t>50-004-011-001490</t>
-  </si>
-  <si>
-    <t>Controfiletto chianina</t>
-  </si>
-  <si>
     <t>50-004-011-000860</t>
   </si>
   <si>
@@ -127,10 +167,10 @@
     <t>Verdure Grigliate</t>
   </si>
   <si>
-    <t>50-004-011-000740</t>
-  </si>
-  <si>
-    <t>Pulled Pork (Con Patate)</t>
+    <t>50-004-011-001921</t>
+  </si>
+  <si>
+    <t>Costata Frollata</t>
   </si>
   <si>
     <t>50-004-011-000570</t>
@@ -139,22 +179,34 @@
     <t>Bistecca Alla Fiorentina In Costata</t>
   </si>
   <si>
+    <t>50-004-011-000610</t>
+  </si>
+  <si>
+    <t>Grigliata Mista Xxl</t>
+  </si>
+  <si>
     <t>50-004-011-001931</t>
   </si>
   <si>
     <t>Costata Frollata 60 Giorni</t>
   </si>
   <si>
+    <t>50-004-011-000700</t>
+  </si>
+  <si>
+    <t>Tagliata Pollo</t>
+  </si>
+  <si>
     <t>50-004-011-001510</t>
   </si>
   <si>
     <t>Salsiccia bovino</t>
   </si>
   <si>
-    <t>50-004-011-000700</t>
-  </si>
-  <si>
-    <t>Tagliata Pollo</t>
+    <t>50-004-011-000580</t>
+  </si>
+  <si>
+    <t>Bistecca Alla Fiorentina Con Filetto</t>
   </si>
   <si>
     <t>50-004-011-000770</t>
@@ -169,12 +221,6 @@
     <t>Salsiccia Toscana (2 Pz.)</t>
   </si>
   <si>
-    <t>50-004-011-000610</t>
-  </si>
-  <si>
-    <t>Grigliata Mista Xxl</t>
-  </si>
-  <si>
     <t>50-004-011-000780</t>
   </si>
   <si>
@@ -187,6 +233,12 @@
     <t xml:space="preserve">Insalata Mista </t>
   </si>
   <si>
+    <t>50-004-011-000720</t>
+  </si>
+  <si>
+    <t>Spuntature Di Suino</t>
+  </si>
+  <si>
     <t>50-004-011-000710</t>
   </si>
   <si>
@@ -199,10 +251,10 @@
     <t>Arrosticini Di Pecora</t>
   </si>
   <si>
-    <t>50-004-011-000720</t>
-  </si>
-  <si>
-    <t>Spuntature Di Suino</t>
+    <t>50-004-011-001500</t>
+  </si>
+  <si>
+    <t>Salsiccia cinta</t>
   </si>
   <si>
     <t>50-004-011-000840</t>
@@ -211,18 +263,18 @@
     <t>Contorno Del Giorno</t>
   </si>
   <si>
+    <t>50-004-011-002110</t>
+  </si>
+  <si>
+    <t>Aggiunta Contorno</t>
+  </si>
+  <si>
     <t>50-004-011-002100</t>
   </si>
   <si>
     <t>Take Away</t>
   </si>
   <si>
-    <t>50-004-011-002110</t>
-  </si>
-  <si>
-    <t>Aggiunta Contorno</t>
-  </si>
-  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -236,6 +288,21 @@
   </si>
   <si>
     <t>12:00-15:59</t>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>04/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>05/01/2025</t>
   </si>
 </sst>
 </file>
@@ -373,7 +440,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -386,13 +453,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -460,7 +541,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n" s="7">
-        <v>788.9817</v>
+        <v>720.2544</v>
       </c>
     </row>
     <row r="9">
@@ -480,27 +561,115 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>2099.93</v>
+      <c r="B11" t="n" s="5">
+        <v>79.6363</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>2238.33</v>
+      <c r="B12" t="n" s="7">
+        <v>15.3636</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>-6.18</v>
+      <c r="B13" t="n" s="5">
+        <v>123.3637</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>233.7911</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>192.4544</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>2675.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>3344.68</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>-20.0</v>
       </c>
     </row>
   </sheetData>
@@ -510,7 +679,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -522,458 +691,509 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>368.2636</v>
+        <v>384.0909</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>6.43</v>
+        <v>25.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>17.54</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>261.1819</v>
+        <v>299.5363</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>17.0</v>
+        <v>5.23</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>12.44</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>202.1818</v>
+        <v>248.1817</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>9.63</v>
+        <v>9.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>176.9091</v>
+        <v>214.8182</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>8.42</v>
+        <v>8.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>152.7272</v>
+        <v>176.9091</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>7.27</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>130.0909</v>
+        <v>163.6363</v>
       </c>
       <c r="D7" t="n" s="5">
         <v>9.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>127.2727</v>
+        <v>145.4546</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>6.06</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>98.1818</v>
+        <v>144.5454</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>27.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>4.68</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>90.9092</v>
+        <v>134.5455</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>20.0</v>
+        <v>37.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>4.33</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>87.2728</v>
+        <v>131.8183</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>6.0</v>
+        <v>29.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>4.16</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
-        <v>72.2545</v>
+        <v>81.4273</v>
       </c>
       <c r="D12" t="n" s="7">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>3.44</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>68.5</v>
+        <v>72.2545</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
-        <v>58.6363</v>
+        <v>70.6365</v>
       </c>
       <c r="D14" t="n" s="7">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E14" t="n" s="7">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>35.1818</v>
+        <v>68.5</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>3.0</v>
+        <v>1.37</v>
       </c>
       <c r="E15" t="n" s="5">
-        <v>1.68</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n" s="7">
-        <v>32.4546</v>
+        <v>58.6364</v>
       </c>
       <c r="D16" t="n" s="7">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E16" t="n" s="7">
-        <v>1.55</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C17" t="n" s="5">
-        <v>27.7273</v>
+        <v>58.6363</v>
       </c>
       <c r="D17" t="n" s="5">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E17" t="n" s="5">
-        <v>1.32</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>23.5455</v>
+        <v>48.2727</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>1.0</v>
+        <v>0.9</v>
       </c>
       <c r="E18" t="n" s="7">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n" s="5">
-        <v>23.4546</v>
+        <v>32.4546</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E19" t="n" s="5">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>16.3636</v>
+        <v>27.7273</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="E20" t="n" s="7">
-        <v>0.78</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" t="n" s="5">
-        <v>15.3636</v>
+        <v>23.4546</v>
       </c>
       <c r="D21" t="n" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E21" t="n" s="5">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C22" t="n" s="7">
-        <v>12.0</v>
+        <v>21.8181</v>
       </c>
       <c r="D22" t="n" s="7">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E22" t="n" s="7">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n" s="5">
-        <v>9.9091</v>
+        <v>19.8182</v>
       </c>
       <c r="D23" t="n" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E23" t="n" s="5">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n" s="7">
-        <v>7.2728</v>
+        <v>15.3636</v>
       </c>
       <c r="D24" t="n" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E24" t="n" s="7">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C25" t="n" s="5">
-        <v>1.3636</v>
+        <v>12.0</v>
       </c>
       <c r="D25" t="n" s="5">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E25" t="n" s="5">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n" s="7">
-        <v>0.9091</v>
+        <v>10.8182</v>
       </c>
       <c r="D26" t="n" s="7">
         <v>1.0</v>
       </c>
       <c r="E26" t="n" s="7">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="1">
-        <v>69</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" t="n" s="1">
-        <v>2099.93</v>
-      </c>
-      <c r="D27" t="n" s="1">
-        <v>175.42</v>
-      </c>
-      <c r="E27" t="n" s="1">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="C27" t="n" s="5">
+        <v>7.2728</v>
+      </c>
+      <c r="D27" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E27" t="n" s="5">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="4">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="4">
+        <v>83</v>
+      </c>
+      <c r="C28" t="n" s="7">
+        <v>1.8182</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="E28" t="n" s="7">
+        <v>0.07</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C29" t="n" s="5">
+        <v>1.3636</v>
+      </c>
+      <c r="D29" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E29" t="n" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="1">
+        <v>86</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" t="n" s="1">
+        <v>2675.81</v>
+      </c>
+      <c r="D30" t="n" s="1">
+        <v>225.81</v>
+      </c>
+      <c r="E30" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -984,7 +1204,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -995,13 +1215,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -1009,15 +1229,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>10.0</v>
@@ -1028,10 +1248,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>2.0</v>
@@ -1042,10 +1262,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>1.0</v>
@@ -1056,10 +1276,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>1.0</v>
@@ -1070,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n" s="1">
         <v>14.0</v>
@@ -1085,15 +1305,15 @@
     <row r="8"/>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>73</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
         <v>26.0</v>
@@ -1104,10 +1324,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
         <v>20.0</v>
@@ -1118,10 +1338,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>17.0</v>
@@ -1132,10 +1352,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n" s="5">
         <v>16.0</v>
@@ -1146,10 +1366,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>14.0</v>
@@ -1160,10 +1380,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C15" t="n" s="5">
         <v>9.0</v>
@@ -1174,10 +1394,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>8.0</v>
@@ -1188,10 +1408,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>7.0</v>
@@ -1202,52 +1422,52 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C18" t="n" s="7">
-        <v>6.43</v>
+        <v>6.0</v>
       </c>
       <c r="D18" t="n" s="7">
-        <v>368.2636</v>
+        <v>87.2728</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>6.0</v>
       </c>
       <c r="D19" t="n" s="5">
-        <v>87.2728</v>
+        <v>16.3636</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C20" t="n" s="7">
-        <v>6.0</v>
+        <v>5.23</v>
       </c>
       <c r="D20" t="n" s="7">
-        <v>16.3636</v>
+        <v>299.5363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>5.0</v>
@@ -1258,10 +1478,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>3.0</v>
@@ -1272,10 +1492,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>3.0</v>
@@ -1286,10 +1506,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="4">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s" s="4">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C24" t="n" s="7">
         <v>2.0</v>
@@ -1300,10 +1520,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C25" t="n" s="5">
         <v>2.0</v>
@@ -1314,10 +1534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="4">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="B26" t="s" s="4">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C26" t="n" s="7">
         <v>2.0</v>
@@ -1328,10 +1548,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C27" t="n" s="5">
         <v>1.62</v>
@@ -1342,10 +1562,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="4">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s" s="4">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C28" t="n" s="7">
         <v>1.37</v>
@@ -1356,10 +1576,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C29" t="n" s="5">
         <v>1.0</v>
@@ -1370,10 +1590,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="4">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s" s="4">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C30" t="n" s="7">
         <v>1.0</v>
@@ -1384,10 +1604,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C31" t="n" s="5">
         <v>1.0</v>
@@ -1398,10 +1618,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="4">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s" s="4">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C32" t="n" s="7">
         <v>1.0</v>
@@ -1412,10 +1632,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C33" t="n" s="5">
         <v>1.0</v>
@@ -1426,10 +1646,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="4">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B34" t="s" s="4">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C34" t="n" s="7">
         <v>1.0</v>
@@ -1440,26 +1660,402 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C35" t="n" s="1">
+        <v>160.22</v>
+      </c>
+      <c r="D35" t="n" s="1">
+        <v>2004.02</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="s" s="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="B38" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C38" t="n" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>76.8181</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C39" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D39" t="n" s="5">
+        <v>18.1818</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="C40" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D40" t="n" s="7">
+        <v>10.9091</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C41" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D41" t="n" s="5">
+        <v>19.0909</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="C42" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D42" t="n" s="7">
+        <v>12.6364</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C43" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D43" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="4">
+        <v>78</v>
+      </c>
+      <c r="B44" t="s" s="4">
+        <v>79</v>
+      </c>
+      <c r="C44" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D44" t="n" s="7">
+        <v>10.8182</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="C45" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D45" t="n" s="5">
+        <v>9.9091</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C46" t="n" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="D46" t="n" s="7">
+        <v>48.2727</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C47" t="n" s="1">
+        <v>17.9</v>
+      </c>
+      <c r="D47" t="n" s="1">
+        <v>218.36</v>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="s" s="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="4">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s" s="4">
+        <v>47</v>
+      </c>
+      <c r="C50" t="n" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="D50" t="n" s="7">
+        <v>25.4546</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="C51" t="n" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="D51" t="n" s="5">
+        <v>22.7273</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="B52" t="s" s="4">
+        <v>35</v>
+      </c>
+      <c r="C52" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D52" t="n" s="7">
+        <v>76.3636</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C53" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D53" t="n" s="5">
+        <v>58.1818</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C54" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D54" t="n" s="7">
+        <v>46.0909</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C55" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D55" t="n" s="5">
+        <v>47.091</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B56" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C56" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D56" t="n" s="7">
+        <v>36.3636</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B57" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="B35" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="C35" t="n" s="1">
-        <v>161.42</v>
-      </c>
-      <c r="D35" t="n" s="1">
-        <v>2072.75</v>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="C57" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D57" t="n" s="5">
+        <v>5.4545</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="4">
+        <v>50</v>
+      </c>
+      <c r="B58" t="s" s="4">
+        <v>51</v>
+      </c>
+      <c r="C58" t="n" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="D58" t="n" s="7">
+        <v>81.4273</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C59" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D59" t="n" s="5">
+        <v>14.4545</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="C60" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D60" t="n" s="7">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="C61" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D61" t="n" s="5">
+        <v>0.9091</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="1">
+        <v>88</v>
+      </c>
+      <c r="B62" t="s" s="4">
+        <v>89</v>
+      </c>
+      <c r="C62" t="n" s="1">
+        <v>33.69</v>
+      </c>
+      <c r="D62" t="n" s="1">
+        <v>426.25</v>
+      </c>
+    </row>
+    <row r="63"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A62:B62"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>4482.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>4653.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>